--- a/agile_sheet.xlsx
+++ b/agile_sheet.xlsx
@@ -556,6 +556,9 @@
     <t xml:space="preserve">3- Completed</t>
   </si>
   <si>
+    <t>US-002</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data Ingestion Layer
 As a data engineer, I want to load raw CSV support tickets, handle missing values, and normalize text formats so that downstream processing has clean data.</t>
   </si>
@@ -569,6 +572,9 @@
     <t>S2</t>
   </si>
   <si>
+    <t>US-003</t>
+  </si>
+  <si>
     <t xml:space="preserve">Entity Extraction Engine
 As an analyst, I want to automatically extract Customer, Product, and Ticket entities from unstructured text to reduce manual tagging.</t>
   </si>
@@ -576,11 +582,17 @@
     <t xml:space="preserve">Data Ingestion Completion</t>
   </si>
   <si>
+    <t>US-004</t>
+  </si>
+  <si>
     <t xml:space="preserve">Graph Construction Hub
 We want structured triples (entity-relation-entity) stored in Neo4j so that complex relationships become queryable.</t>
   </si>
   <si>
     <t xml:space="preserve">Entity Extraction Engine</t>
+  </si>
+  <si>
+    <t>US-005</t>
   </si>
   <si>
     <t xml:space="preserve">Rich Context Engineering
@@ -593,6 +605,9 @@
     <t>S3</t>
   </si>
   <si>
+    <t>US-006</t>
+  </si>
+  <si>
     <t xml:space="preserve">Embedding Generation
 As a system, I want to generate mathematical vectors for graph data using Hugging Face models so that semantic meaning is captured.</t>
   </si>
@@ -600,11 +615,17 @@
     <t xml:space="preserve">Rich Context Engineering</t>
   </si>
   <si>
+    <t>US-007</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vector Indexing
 As a developer, I want to build a native Vector Index inside Neo4j so that we avoid external dependencies like FAISS.</t>
   </si>
   <si>
     <t xml:space="preserve">Embedding Generation</t>
+  </si>
+  <si>
+    <t>US-008</t>
   </si>
   <si>
     <t xml:space="preserve">Graph RAG Pipeline
@@ -617,6 +638,9 @@
     <t>S4</t>
   </si>
   <si>
+    <t>US-009</t>
+  </si>
+  <si>
     <t xml:space="preserve">Analytics Dashboard
 As a manager, I want a web interface with live database statistics so that I can monitor total tickets, unique customers, and product trends in real-time.</t>
   </si>
@@ -624,11 +648,14 @@
     <t xml:space="preserve">Graph RAG Pipeline</t>
   </si>
   <si>
+    <t>US-010</t>
+  </si>
+  <si>
     <t xml:space="preserve">Conversational UI
 As a non-technical user, I want an interactive chat interface to ask data questions in plain English so that I don't need to write Cypher queries.</t>
   </si>
   <si>
-    <t xml:space="preserve">US-001           </t>
+    <t xml:space="preserve">US-011           </t>
   </si>
   <si>
     <t xml:space="preserve">Cloud Deployment
@@ -731,9 +758,6 @@
     <t>Design</t>
   </si>
   <si>
-    <t>US-002</t>
-  </si>
-  <si>
     <t xml:space="preserve">Write normalize_tickets.py to handle missing values and nulls.</t>
   </si>
   <si>
@@ -743,13 +767,7 @@
     <t xml:space="preserve">Normalize text strings to prevent duplicate graph nodes and test output.</t>
   </si>
   <si>
-    <t>US-003</t>
-  </si>
-  <si>
     <t xml:space="preserve">Develop entity_extractor.py to map rows to Customer, Product, Ticket entities.</t>
-  </si>
-  <si>
-    <t>US-004</t>
   </si>
   <si>
     <t xml:space="preserve">Configure Neo4j AuraDB credentials and establish connection.</t>
@@ -758,25 +776,13 @@
     <t xml:space="preserve">Write graph_builder.py Cypher queries using MERGE logic.</t>
   </si>
   <si>
-    <t>US-005</t>
-  </si>
-  <si>
     <t xml:space="preserve">Implement "Rich Context" string concatenation for AI optimization.</t>
-  </si>
-  <si>
-    <t>US-006</t>
   </si>
   <si>
     <t xml:space="preserve">Integrate Hugging Face all-MiniLM-L6-v2 for embeddings.</t>
   </si>
   <si>
-    <t>US-007</t>
-  </si>
-  <si>
     <t xml:space="preserve">Script create_vector_index.py to index data natively in Neo4j.</t>
-  </si>
-  <si>
-    <t>US-008</t>
   </si>
   <si>
     <t xml:space="preserve">Develop LangChain retrieval pipeline (rag_agent.py) with Llama-3.</t>
@@ -788,13 +794,7 @@
     <t xml:space="preserve">Integration Test</t>
   </si>
   <si>
-    <t>US-009</t>
-  </si>
-  <si>
     <t xml:space="preserve">Build app.py Streamlit layout and extract live Neo4j metrics.</t>
-  </si>
-  <si>
-    <t>US-010</t>
   </si>
   <si>
     <t xml:space="preserve">Implement interactive iMessage-style chat UI and connect to RAG.</t>
@@ -837,7 +837,6 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve">Project Discussion &amp; Preprocessing:</t>
@@ -845,7 +844,6 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve"> Need a robust strategy for handling noisy enterprise data (NaNs, mismatched types) before it hits the NLP pipeline.</t>
@@ -859,7 +857,6 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve">Data Cleaning:</t>
@@ -867,7 +864,6 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve"> Preprocessing phase was failing to catch trailing whitespaces, creating a risk of duplicate nodes in the future graph.</t>
@@ -884,7 +880,6 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve">Entity Extraction:</t>
@@ -892,7 +887,6 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve"> Challenges in defining the logic to parse unstructured ticket text into clean subject-predicate-object triples.</t>
@@ -909,7 +903,6 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve">Graph Modeling:</t>
@@ -917,7 +910,6 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve"> Cypher query inefficiencies causing bottlenecks and potential data duplication during graph construction.</t>
@@ -937,7 +929,6 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve">Embedding Extraction:</t>
@@ -945,7 +936,6 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve"> Needed to finalize the vectorization strategy to capture semantic meaning rather than relying on keyword matching.</t>
@@ -962,7 +952,6 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve">Model Enhancement &amp; Indexing:</t>
@@ -970,7 +959,6 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve"> Neo4j vector indexing was retaining stale embeddings during iterative testing, skewing search results.</t>
@@ -990,7 +978,6 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve">Context Injection:</t>
@@ -998,7 +985,6 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve"> The RAG pipeline suffered from fragmented context, causing the LLM to hallucinate during hybrid search retrieval.</t>
@@ -1015,7 +1001,6 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve">Deployment Bottleneck:</t>
@@ -1023,7 +1008,6 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Liberation Sans"/>
       </rPr>
       <t xml:space="preserve"> Cloud deployment failed due to the massive 800MB+ memory footprint of the default PyTorch GPU dependencies.</t>
@@ -1119,10 +1103,10 @@
     <numFmt numFmtId="164" formatCode="[$-1009]d/mmm/yy"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="10.000000"/>
-      <color indexed="64"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1132,7 +1116,6 @@
     <font>
       <b/>
       <sz val="8.000000"/>
-      <color indexed="64"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1140,18 +1123,11 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.000000"/>
-      <color indexed="64"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="8.000000"/>
-      <color indexed="64"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="9.000000"/>
-      <color indexed="64"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1163,24 +1139,20 @@
     <font>
       <b/>
       <sz val="12.000000"/>
-      <color indexed="64"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="12.000000"/>
-      <color indexed="64"/>
       <name val="Liberation Sans"/>
     </font>
     <font>
       <sz val="12.000000"/>
-      <color indexed="64"/>
       <name val="Liberation Sans"/>
     </font>
     <font>
       <b/>
       <sz val="10.000000"/>
-      <color indexed="64"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -1234,7 +1206,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -1367,21 +1339,6 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
       <left style="none"/>
       <right style="thin">
         <color theme="1"/>
@@ -1447,44 +1404,44 @@
     <xf fontId="3" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="3" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="0">
+    <xf fontId="3" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="3" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="0">
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="5" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -1504,7 +1461,7 @@
       <alignment vertical="center"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="0">
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="2" fillId="4" borderId="8" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1531,7 +1488,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -1539,19 +1496,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="8" fillId="6" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="7" fillId="6" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="8" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="11" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="8" fillId="0" borderId="2" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="11" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="8" fillId="0" borderId="2" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -1559,19 +1516,19 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="9" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="11" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="9" fillId="0" borderId="2" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="11" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="9" fillId="0" borderId="2" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="11" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="9" fillId="0" borderId="2" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -1579,7 +1536,7 @@
       <alignment vertical="center"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -1587,7 +1544,7 @@
       <alignment wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="4" fillId="0" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -1595,7 +1552,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -1607,15 +1564,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -1623,27 +1580,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="0">
       <alignment wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
       <alignment wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -1651,10 +1608,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="11" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="0">
+    <xf fontId="10" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="11" fillId="8" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="10" fillId="8" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -1690,7 +1647,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName=" " id="{E9AD669B-5789-22F0-0BD8-202371EFE774}"/>
+  <person displayName=" " id="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}"/>
 </personList>
 </file>
 
@@ -2086,7 +2043,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="F1" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{001E00B5-00BE-4CF0-85AF-007200D900F1}" done="0">
+  <threadedComment ref="F1" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{001E00B5-00BE-4CF0-85AF-007200D900F1}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZQo
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
@@ -2098,7 +2055,7 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D2" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{008B005F-0081-4DF8-9822-00ED00BD00EA}" done="0">
+  <threadedComment ref="D2" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{008B005F-0081-4DF8-9822-00ED00BD00EA}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZRI
 Please enter the dates in either of these formats    (2025-01-27 09:44:41)
@@ -2106,7 +2063,7 @@
 15-Sep-2016
 </text>
   </threadedComment>
-  <threadedComment ref="E2" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{0067002B-000B-4107-B6B0-00BE005100D6}" done="0">
+  <threadedComment ref="E2" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{0067002B-000B-4107-B6B0-00BE005100D6}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZRU
 Please enter the dates in either of these formats    (2025-01-27 09:44:41)
@@ -2114,105 +2071,105 @@
 15-Sep-2016
 </text>
   </threadedComment>
-  <threadedComment ref="K3" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{00AF00F3-00E4-43BD-A8FD-00B100D20040}" done="0">
+  <threadedComment ref="K3" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{00AF00F3-00E4-43BD-A8FD-00B100D20040}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZRg
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
 Pending effort hours after completion of day 2 work
 </text>
   </threadedComment>
-  <threadedComment ref="L3" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{000F00CB-0014-4924-8485-005F006600BD}" done="0">
+  <threadedComment ref="L3" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{000F00CB-0014-4924-8485-005F006600BD}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZQs
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
 Pending effort hours after completion of day 3 work
 </text>
   </threadedComment>
-  <threadedComment ref="M3" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{00100056-0013-4C3A-B063-00B300B900D2}" done="0">
+  <threadedComment ref="M3" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{00100056-0013-4C3A-B063-00B300B900D2}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZRo
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
 Pending effort hours after completion of day 4 work
 </text>
   </threadedComment>
-  <threadedComment ref="N3" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{006000D3-0024-4720-B368-00F800140064}" done="0">
+  <threadedComment ref="N3" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{006000D3-0024-4720-B368-00F800140064}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZQw
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
 Pending effort hours after completion of day 5 work
 </text>
   </threadedComment>
-  <threadedComment ref="O3" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{00250063-00C7-4568-BC70-00D3008400F6}" done="0">
+  <threadedComment ref="O3" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{00250063-00C7-4568-BC70-00D3008400F6}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZRk
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
 Pending effort hours after completion of day 6 work
 </text>
   </threadedComment>
-  <threadedComment ref="P3" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{00A80060-009E-44D6-B57B-00D200C2002D}" done="0">
+  <threadedComment ref="P3" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{00A80060-009E-44D6-B57B-00D200C2002D}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZRY
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
 Pending effort hours after completion of day 7 work
 </text>
   </threadedComment>
-  <threadedComment ref="Q3" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{008B00A1-00C9-4627-8AB0-007300140057}" done="0">
+  <threadedComment ref="Q3" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{008B00A1-00C9-4627-8AB0-007300140057}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZRA
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
 Pending effort hours after completion of day 8 work
 </text>
   </threadedComment>
-  <threadedComment ref="R3" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{00B4005D-00C9-4FBD-B413-00F6009900DD}" done="0">
+  <threadedComment ref="R3" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{00B4005D-00C9-4FBD-B413-00F6009900DD}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZRs
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
 Pending effort hours after completion of day 9 work
 </text>
   </threadedComment>
-  <threadedComment ref="S3" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{002500DC-00CB-40F8-8FB1-00680031004E}" done="0">
+  <threadedComment ref="S3" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{002500DC-00CB-40F8-8FB1-00680031004E}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZRM
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
 Pending effort hours after completion of day 10 work
 </text>
   </threadedComment>
-  <threadedComment ref="T3" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{00A3000C-00D7-4B4C-BF2E-007600AE008D}" done="0">
+  <threadedComment ref="T3" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{00A3000C-00D7-4B4C-BF2E-007600AE008D}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZRE
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
 Pending effort hours after completion of day 11 work
 </text>
   </threadedComment>
-  <threadedComment ref="U3" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{0025009D-00D5-4748-8CFC-0034007F00EB}" done="0">
+  <threadedComment ref="U3" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{0025009D-00D5-4748-8CFC-0034007F00EB}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZQ8
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
 Pending effort hours after completion of day 12 work
 </text>
   </threadedComment>
-  <threadedComment ref="V3" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{00AB00E0-0080-4D5D-9BBB-00230093006F}" done="0">
+  <threadedComment ref="V3" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{00AB00E0-0080-4D5D-9BBB-00230093006F}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZQ0
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
 Pending effort hours after completion of day 13 work
 </text>
   </threadedComment>
-  <threadedComment ref="W3" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{00A000CE-003D-4613-9AFD-0061004800B1}" done="0">
+  <threadedComment ref="W3" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{00A000CE-003D-4613-9AFD-0061004800B1}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZRQ
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
 Pending effort hours after completion of day 14 work
 </text>
   </threadedComment>
-  <threadedComment ref="I3" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{000700DC-0010-471C-AF2F-0004004500EC}" done="0">
+  <threadedComment ref="I3" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{000700DC-0010-471C-AF2F-0004004500EC}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZQ4
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
 This is the total task estimated in hours for all the user stories
 </text>
   </threadedComment>
-  <threadedComment ref="J3" personId="{E9AD669B-5789-22F0-0BD8-202371EFE774}" id="{005500FC-00B6-42E6-92F0-00190010008F}" done="0">
+  <threadedComment ref="J3" personId="{80FA083C-89A8-4B23-7D42-8A9816BC5C93}" id="{005500FC-00B6-42E6-92F0-00190010008F}" done="0">
     <text xml:space="preserve">======
 ID#AAABcShYZRc
 Sumeet Kumar Barua08    (2025-01-27 09:44:41)
@@ -2302,19 +2259,19 @@
         <v>8</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
@@ -2322,22 +2279,22 @@
     </row>
     <row r="4" ht="70.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>13</v>
@@ -2348,25 +2305,25 @@
     </row>
     <row r="5" ht="78" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>14</v>
@@ -2374,22 +2331,22 @@
     </row>
     <row r="6" ht="68.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>13</v>
@@ -2400,22 +2357,22 @@
     </row>
     <row r="7" ht="63.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>13</v>
@@ -2426,22 +2383,22 @@
     </row>
     <row r="8" ht="69" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>13</v>
@@ -2452,25 +2409,25 @@
     </row>
     <row r="9" ht="75.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>14</v>
@@ -2478,22 +2435,22 @@
     </row>
     <row r="10" ht="66" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>13</v>
@@ -2504,25 +2461,25 @@
     </row>
     <row r="11" ht="77.25" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>14</v>
@@ -2530,25 +2487,25 @@
     </row>
     <row r="12" ht="69" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>14</v>
@@ -3893,7 +3850,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00A20079-0088-46C9-95F9-006000CB00C7}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00C90075-00F5-4B87-8A3B-00CE00B70040}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"MUST HAVE,SHOULD HAVE,COULD HAVE,WON'T HAVE"</xm:f>
           </x14:formula1>
@@ -3902,7 +3859,7 @@
           </x14:formula2>
           <xm:sqref>E13:E50</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00A300DE-00A2-4F51-B2FE-009A009100F9}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{000900BA-0092-46FD-A3D9-004500B1000A}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"1- Not Started,2- In Progress,3- Completed"</xm:f>
           </x14:formula1>
@@ -3911,13 +3868,13 @@
           </x14:formula2>
           <xm:sqref>H13:H50</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00BD0008-00D9-48AD-91D1-001000190059}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{005000F2-0063-49C0-9F61-00CF005700AC}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"1- Not Started"</xm:f>
           </x14:formula1>
           <xm:sqref>H2:H12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{000800BC-00CD-4E41-AECB-0049000A0076}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00810053-005B-4540-8BA8-0001005C0046}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"MUST HAVE"</xm:f>
           </x14:formula1>
@@ -3955,7 +3912,7 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -3988,70 +3945,70 @@
         <v>2</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H2" s="25" t="s">
         <v>7</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="L2" s="28" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N2" s="28" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="O2" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="P2" s="28" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="Q2" s="28" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="R2" s="28" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="S2" s="28" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="T2" s="28" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="U2" s="28" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="V2" s="28" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="W2" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="X2" s="29"/>
       <c r="Y2" s="29"/>
@@ -4132,7 +4089,7 @@
     </row>
     <row r="4" ht="33.75" customHeight="1">
       <c r="A4" s="31" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B4" s="31"/>
       <c r="C4" s="31"/>
@@ -4165,55 +4122,55 @@
         <v>2</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H5" s="32" t="s">
         <v>7</v>
       </c>
       <c r="I5" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="M5" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="N5" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="O5" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="P5" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="K5" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="L5" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="M5" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="N5" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="O5" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="P5" s="32" t="s">
-        <v>55</v>
-      </c>
       <c r="Q5" s="32" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="R5" s="32" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="S5" s="35"/>
       <c r="T5" s="35"/>
@@ -4232,7 +4189,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D6" s="38">
         <v>46027</v>
@@ -4244,7 +4201,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H6" s="36" t="s">
         <v>14</v>
@@ -4296,7 +4253,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D7" s="38">
         <v>46028</v>
@@ -4305,10 +4262,10 @@
         <v>46029</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H7" s="36" t="s">
         <v>14</v>
@@ -4354,13 +4311,13 @@
     </row>
     <row r="8" ht="57" customHeight="1">
       <c r="A8" s="36" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="B8" s="36">
         <v>3</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D8" s="38">
         <v>46030</v>
@@ -4369,10 +4326,10 @@
         <v>46034</v>
       </c>
       <c r="F8" s="36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H8" s="36" t="s">
         <v>14</v>
@@ -4418,13 +4375,13 @@
     </row>
     <row r="9" ht="57" customHeight="1">
       <c r="A9" s="36" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="B9" s="36">
         <v>4</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D9" s="37">
         <v>46034</v>
@@ -4436,7 +4393,7 @@
         <v>13</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H9" s="36" t="s">
         <v>14</v>
@@ -4482,13 +4439,13 @@
     </row>
     <row r="10" ht="57" customHeight="1">
       <c r="A10" s="36" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="B10" s="36">
         <v>5</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D10" s="37">
         <v>46041</v>
@@ -4500,7 +4457,7 @@
         <v>13</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H10" s="36" t="s">
         <v>14</v>
@@ -4546,13 +4503,13 @@
     </row>
     <row r="11" ht="57" customHeight="1">
       <c r="A11" s="36" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="B11" s="36">
         <v>6</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D11" s="37">
         <v>46043</v>
@@ -4561,10 +4518,10 @@
         <v>46044</v>
       </c>
       <c r="F11" s="36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H11" s="36" t="s">
         <v>14</v>
@@ -4610,13 +4567,13 @@
     </row>
     <row r="12" ht="57" customHeight="1">
       <c r="A12" s="36" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="B12" s="36">
         <v>7</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D12" s="37">
         <v>46044</v>
@@ -4625,10 +4582,10 @@
         <v>46048</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H12" s="36" t="s">
         <v>14</v>
@@ -4674,13 +4631,13 @@
     </row>
     <row r="13" ht="57" customHeight="1">
       <c r="A13" s="36" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="B13" s="36">
         <v>8</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D13" s="37">
         <v>46048</v>
@@ -4692,7 +4649,7 @@
         <v>13</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H13" s="36" t="s">
         <v>14</v>
@@ -4738,13 +4695,13 @@
     </row>
     <row r="14" ht="57" customHeight="1">
       <c r="A14" s="36" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="B14" s="36">
         <v>9</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D14" s="37">
         <v>46055</v>
@@ -4753,10 +4710,10 @@
         <v>46057</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H14" s="36" t="s">
         <v>14</v>
@@ -4802,13 +4759,13 @@
     </row>
     <row r="15" ht="57" customHeight="1">
       <c r="A15" s="36" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="B15" s="36">
         <v>10</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D15" s="37">
         <v>46057</v>
@@ -4820,7 +4777,7 @@
         <v>13</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H15" s="36" t="s">
         <v>14</v>
@@ -4866,13 +4823,13 @@
     </row>
     <row r="16" ht="57" customHeight="1">
       <c r="A16" s="36" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="B16" s="36">
         <v>11</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D16" s="37">
         <v>46059</v>
@@ -4881,10 +4838,10 @@
         <v>46063</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H16" s="36" t="s">
         <v>14</v>
@@ -4930,13 +4887,13 @@
     </row>
     <row r="17" ht="57" customHeight="1">
       <c r="A17" s="36" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="B17" s="36">
         <v>12</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D17" s="37">
         <v>46063</v>
@@ -4948,7 +4905,7 @@
         <v>13</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H17" s="36" t="s">
         <v>14</v>
@@ -4994,13 +4951,13 @@
     </row>
     <row r="18" ht="57" customHeight="1">
       <c r="A18" s="36" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="B18" s="36">
         <v>13</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D18" s="37">
         <v>46069</v>
@@ -5012,7 +4969,7 @@
         <v>13</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H18" s="36" t="s">
         <v>14</v>
@@ -5058,7 +5015,7 @@
     </row>
     <row r="19" ht="57" customHeight="1">
       <c r="A19" s="36" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="B19" s="36">
         <v>14</v>
@@ -5073,10 +5030,10 @@
         <v>46073</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H19" s="36" t="s">
         <v>14</v>
@@ -5122,7 +5079,7 @@
     </row>
     <row r="20" ht="57" customHeight="1">
       <c r="A20" s="36" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="B20" s="36">
         <v>15</v>
@@ -5137,10 +5094,10 @@
         <v>46076</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H20" s="36" t="s">
         <v>14</v>
@@ -5204,7 +5161,7 @@
         <v>13</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H21" s="36" t="s">
         <v>14</v>
@@ -32230,7 +32187,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8" disablePrompts="0">
-        <x14:dataValidation xr:uid="{009E0003-00B5-4FA5-8173-003C001D0098}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00210062-0096-4817-908F-002100220012}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"Build,Coding,Design,Integration Test,Regression Test,System Test,Unit Test,Others"</xm:f>
           </x14:formula1>
@@ -32239,7 +32196,7 @@
           </x14:formula2>
           <xm:sqref>G22:G52</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{0098003B-001F-4E3F-80E3-0041009D0046}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00E7004E-003A-423A-9B69-007F00A80047}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"1- Not Started,2- In Progress,3- Completed"</xm:f>
           </x14:formula1>
@@ -32248,7 +32205,7 @@
           </x14:formula2>
           <xm:sqref>H22:H52</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{009A00A2-0056-4A24-BBC9-004E004B0038}" type="decimal" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00C600A1-006D-4180-A358-007B001D0091}" type="decimal" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>0</xm:f>
           </x14:formula1>
@@ -32257,7 +32214,7 @@
           </x14:formula2>
           <xm:sqref>I22:I52</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{005000AA-0069-43B8-9394-00AD00EB0060}" type="decimal" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="lessThanOrEqual" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{0010008B-00EB-4BFE-951A-009700A300C9}" type="decimal" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="lessThanOrEqual" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>M21</xm:f>
           </x14:formula1>
@@ -32266,7 +32223,7 @@
           </x14:formula2>
           <xm:sqref>S5:W8 S9:W9 S10:W21 I22:W22 R23:W25 J26:W69 J53:L53</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00E200CA-00B5-4E9C-B5F4-00B100E60086}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{008A0045-000C-4A42-88AF-00AA00AC000D}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"Build,Unit Test,System Test,Coding,General,Integration"</xm:f>
           </x14:formula1>
@@ -32275,7 +32232,7 @@
           </x14:formula2>
           <xm:sqref>G53</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{0064002A-00B5-4B2B-858C-007A000C0052}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{009000D6-001C-45FE-B53D-00CE00C400B4}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>Status</xm:f>
           </x14:formula1>
@@ -32284,7 +32241,7 @@
           </x14:formula2>
           <xm:sqref>H53 H90:H983</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{003000BE-00EC-42CF-9198-004900790000}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00870080-0083-4ABE-AA72-00E100510039}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>Team</xm:f>
           </x14:formula1>
@@ -32293,7 +32250,7 @@
           </x14:formula2>
           <xm:sqref>F90:F983</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{005B00E0-007C-4CD5-87C0-00D2006B00D7}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{000F0034-001C-4D02-A7D0-009100170026}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="equal" prompt=" - " showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>Category</xm:f>
           </x14:formula1>
@@ -32358,7 +32315,7 @@
         <v>103</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C3" s="36" t="s">
         <v>104</v>
@@ -32372,7 +32329,7 @@
         <v>103</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C4" s="36" t="s">
         <v>106</v>
@@ -32386,7 +32343,7 @@
         <v>108</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>109</v>
